--- a/penaltyTable.xlsx
+++ b/penaltyTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michael/Desktop/TAOR/TAOR-Group-Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erinfortin/TAOR-Group-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F3E0F9-77A3-B54E-8A2F-3FF4BCE0EE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2856DF26-16B8-264B-968E-3F498B80B2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="620" windowWidth="28040" windowHeight="16340" xr2:uid="{B59AE534-77ED-3B48-A6E6-F9A0ADAA2FA8}"/>
+    <workbookView xWindow="1300" yWindow="1080" windowWidth="28040" windowHeight="16340" xr2:uid="{B59AE534-77ED-3B48-A6E6-F9A0ADAA2FA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Monday 09:00</t>
   </si>
@@ -164,43 +164,13 @@
     <t>Monday 17:00</t>
   </si>
   <si>
-    <t>Monday 18:00</t>
-  </si>
-  <si>
-    <t>Tuesday 18:00</t>
-  </si>
-  <si>
     <t>Wednesday 16:00</t>
   </si>
   <si>
     <t>Wednesday 17:00</t>
   </si>
   <si>
-    <t>Wednesday 18:00</t>
-  </si>
-  <si>
     <t>Thursday 17:00</t>
-  </si>
-  <si>
-    <t>Thursday 18:00</t>
-  </si>
-  <si>
-    <t>Friday 18:00</t>
-  </si>
-  <si>
-    <t>Monday 08:00</t>
-  </si>
-  <si>
-    <t>Tuesday 08:00</t>
-  </si>
-  <si>
-    <t>Wednesday 08:00</t>
-  </si>
-  <si>
-    <t>Thursday 08:00</t>
-  </si>
-  <si>
-    <t>Friday 08:00</t>
   </si>
 </sst>
 </file>
@@ -256,9 +226,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -296,7 +266,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -402,7 +372,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -544,7 +514,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -552,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EB0989-33D3-994B-A3C5-0D3624936C9C}">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -560,175 +530,175 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="B1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>18</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B19">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>70</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B21">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -736,39 +706,39 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -776,31 +746,31 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B28">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B29">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B30">
-        <v>100</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -808,95 +778,95 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B32">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B33">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B34">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B37">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B38">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B39">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B40">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B41">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B42">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B43">
         <v>100</v>
@@ -904,7 +874,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B44">
         <v>100</v>
@@ -912,89 +882,9 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B45">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55">
         <v>100</v>
       </c>
     </row>

--- a/penaltyTable.xlsx
+++ b/penaltyTable.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erinfortin/TAOR-Group-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2856DF26-16B8-264B-968E-3F498B80B2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FC8115-D118-574A-8C4A-939A1569D07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1300" yWindow="1080" windowWidth="28040" windowHeight="16340" xr2:uid="{B59AE534-77ED-3B48-A6E6-F9A0ADAA2FA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -541,7 +541,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -549,7 +549,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -565,7 +565,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -573,7 +573,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -581,7 +581,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -589,7 +589,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>70</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -605,7 +605,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -613,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -621,7 +621,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -645,7 +645,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -653,7 +653,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -661,7 +661,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>60</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -677,7 +677,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -685,7 +685,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -693,7 +693,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -709,7 +709,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -717,7 +717,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -749,7 +749,7 @@
         <v>24</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -757,7 +757,7 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -765,7 +765,7 @@
         <v>26</v>
       </c>
       <c r="B30">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -781,7 +781,7 @@
         <v>28</v>
       </c>
       <c r="B32">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -789,7 +789,7 @@
         <v>29</v>
       </c>
       <c r="B33">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -797,7 +797,7 @@
         <v>30</v>
       </c>
       <c r="B34">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -805,7 +805,7 @@
         <v>31</v>
       </c>
       <c r="B35">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -821,7 +821,7 @@
         <v>32</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -829,7 +829,7 @@
         <v>33</v>
       </c>
       <c r="B38">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -837,7 +837,7 @@
         <v>34</v>
       </c>
       <c r="B39">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -845,7 +845,7 @@
         <v>35</v>
       </c>
       <c r="B40">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
